--- a/backtest_runs/20260410_193731/by_symbol/AKDHL/AKDHL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AKDHL/AKDHL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1232</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>98768</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>98768</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>102724.48</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>119198.08</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>119198.08</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>121267.84</v>
